--- a/output/pdf_financials_xlsx/PINE.UN.xlsx
+++ b/output/pdf_financials_xlsx/PINE.UN.xlsx
@@ -953,7 +953,7 @@
         <v>0.046042</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.04023</v>
+        <v>-0.04023</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.255408</v>
@@ -1113,7 +1113,7 @@
         <v>0.046042</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.04023</v>
+        <v>-0.04023</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.255408</v>
@@ -1212,7 +1212,7 @@
         <v>0.046042</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.04023</v>
+        <v>-0.04023</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.255408</v>
@@ -1386,7 +1386,7 @@
         <v>0.046042</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.04023</v>
+        <v>-0.04023</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.255408</v>
@@ -1452,7 +1452,7 @@
         <v>0.046042</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.04023</v>
+        <v>-0.04023</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.255408</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -9864,7 +9864,7 @@
         </is>
       </c>
       <c r="K93" s="5" t="n">
-        <v>0.04023</v>
+        <v>-0.04023</v>
       </c>
       <c r="L93" s="5" t="n">
         <v>-0.255408</v>

--- a/output/pdf_financials_xlsx/PINE.UN.xlsx
+++ b/output/pdf_financials_xlsx/PINE.UN.xlsx
@@ -1595,28 +1595,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.163707</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.050013</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.160861</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.186067</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.08132399999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.122614</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.162582</v>
       </c>
     </row>
     <row r="35">
@@ -1657,28 +1657,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.163707</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.050013</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.160861</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.186067</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.08132399999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.122614</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.162582</v>
       </c>
     </row>
     <row r="37">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
@@ -9674,7 +9674,11 @@
           <t>General and administrative expenses (note 8(b) and (c))</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PINE.UN.xlsx
+++ b/output/pdf_financials_xlsx/PINE.UN.xlsx
@@ -7136,7 +7136,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
